--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128995395</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128998433</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R6" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R7" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>128998409</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128995400</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128995419</v>
+        <v>128995384</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Kistmyran, Kistmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489280</v>
+        <v>489302</v>
       </c>
       <c r="R10" t="n">
-        <v>6834826</v>
+        <v>6834844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128995384</v>
+        <v>128995655</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,17 +1579,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kistmyran, Kistmyran, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489302</v>
+        <v>489289</v>
       </c>
       <c r="R11" t="n">
-        <v>6834844</v>
+        <v>6834834</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128995655</v>
+        <v>128995419</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489289</v>
+        <v>489280</v>
       </c>
       <c r="R12" t="n">
-        <v>6834834</v>
+        <v>6834826</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128998383</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128995366</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>78700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78700</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B6" t="n">
         <v>79034</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R6" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B7" t="n">
         <v>79034</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R7" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128998433</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128995395</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R6" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R7" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128998409</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128995419</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128995384</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128995655</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R15" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R16" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>78701</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>78701</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128998433</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128995395</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R6" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R7" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128998409</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128995419</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128995384</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128995655</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R15" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R16" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>78705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78705</v>
+        <v>97547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R6" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B7" t="n">
         <v>79039</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R7" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R15" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R16" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128998433</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128995395</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>78705</v>
+        <v>97549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>78707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>128998457</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128995378</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128998409</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128995419</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128995384</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128995655</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128995366</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128998383</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>78707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78707</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>78707</v>
+        <v>97576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>97575</v>
+        <v>78707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R6" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R7" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R15" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R16" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128998433</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128995395</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128995378</v>
+        <v>128998457</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489326</v>
+        <v>489265</v>
       </c>
       <c r="R6" t="n">
-        <v>6834820</v>
+        <v>6834875</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128998457</v>
+        <v>128995378</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489265</v>
+        <v>489326</v>
       </c>
       <c r="R7" t="n">
-        <v>6834875</v>
+        <v>6834820</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128998409</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128995419</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128995384</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128995655</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R15" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R16" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>78709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78709</v>
+        <v>97581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128998433</v>
+        <v>128995395</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489243</v>
+        <v>489347</v>
       </c>
       <c r="R2" t="n">
-        <v>6834808</v>
+        <v>6834868</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128995395</v>
+        <v>128998433</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489347</v>
+        <v>489243</v>
       </c>
       <c r="R3" t="n">
-        <v>6834868</v>
+        <v>6834808</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>78709</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>97581</v>
+        <v>78710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>128998457</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128995378</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128998409</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128995419</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128995384</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128995655</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128995367</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128995366</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128998383</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128998305</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128995421</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128995395</v>
+        <v>128998433</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489347</v>
+        <v>489243</v>
       </c>
       <c r="R2" t="n">
-        <v>6834868</v>
+        <v>6834808</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128998433</v>
+        <v>128995395</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489243</v>
+        <v>489347</v>
       </c>
       <c r="R3" t="n">
-        <v>6834808</v>
+        <v>6834868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>78710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78710</v>
+        <v>97587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R15" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R16" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R15" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R16" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>97595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B5" t="n">
-        <v>97595</v>
+        <v>78710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R15" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R16" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998383</v>
+        <v>128995366</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489275</v>
+        <v>489324</v>
       </c>
       <c r="R15" t="n">
-        <v>6834885</v>
+        <v>6834819</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128995366</v>
+        <v>128998383</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489324</v>
+        <v>489275</v>
       </c>
       <c r="R16" t="n">
-        <v>6834819</v>
+        <v>6834885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998567</v>
+        <v>128998544</v>
       </c>
       <c r="B4" t="n">
-        <v>97595</v>
+        <v>78710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489221</v>
+        <v>489284</v>
       </c>
       <c r="R4" t="n">
-        <v>6834826</v>
+        <v>6834754</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998544</v>
+        <v>128998567</v>
       </c>
       <c r="B5" t="n">
-        <v>78710</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489284</v>
+        <v>489221</v>
       </c>
       <c r="R5" t="n">
-        <v>6834754</v>
+        <v>6834826</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128998433</v>
+        <v>128998544</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489243</v>
+        <v>489284</v>
       </c>
       <c r="R2" t="n">
-        <v>6834808</v>
+        <v>6834754</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128995395</v>
+        <v>128995366</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489347</v>
+        <v>489324</v>
       </c>
       <c r="R3" t="n">
-        <v>6834868</v>
+        <v>6834819</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128998544</v>
+        <v>128995367</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Kistmyran, Kistmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489284</v>
+        <v>489318</v>
       </c>
       <c r="R4" t="n">
-        <v>6834754</v>
+        <v>6834835</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128998567</v>
+        <v>128995378</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489221</v>
+        <v>489326</v>
       </c>
       <c r="R5" t="n">
-        <v>6834826</v>
+        <v>6834820</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128998457</v>
+        <v>128995384</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1094,17 +1094,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Kistmyran, Kistmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489265</v>
+        <v>489302</v>
       </c>
       <c r="R6" t="n">
-        <v>6834875</v>
+        <v>6834844</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,26 +1148,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128995378</v>
+        <v>128995395</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489326</v>
+        <v>489347</v>
       </c>
       <c r="R7" t="n">
-        <v>6834820</v>
+        <v>6834868</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,11 +1260,11 @@
         <v>128995400</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1354,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128998409</v>
+        <v>128995419</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489281</v>
+        <v>489280</v>
       </c>
       <c r="R9" t="n">
-        <v>6834874</v>
+        <v>6834826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,26 +1439,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128995419</v>
+        <v>128995421</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489280</v>
+        <v>489351</v>
       </c>
       <c r="R10" t="n">
-        <v>6834826</v>
+        <v>6834863</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,26 +1536,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128995384</v>
+        <v>128995655</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1579,17 +1579,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kistmyran, Kistmyran, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489302</v>
+        <v>489289</v>
       </c>
       <c r="R11" t="n">
-        <v>6834844</v>
+        <v>6834834</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128995655</v>
+        <v>128998305</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489289</v>
+        <v>489249</v>
       </c>
       <c r="R12" t="n">
-        <v>6834834</v>
+        <v>6834885</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1745,11 +1745,11 @@
         <v>128998360</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1839,14 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128995367</v>
+        <v>128998383</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1870,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kistmyran, Kistmyran, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489318</v>
+        <v>489275</v>
       </c>
       <c r="R14" t="n">
-        <v>6834835</v>
+        <v>6834885</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,26 +1924,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128995366</v>
+        <v>128998409</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489324</v>
+        <v>489281</v>
       </c>
       <c r="R15" t="n">
-        <v>6834819</v>
+        <v>6834874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,14 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998383</v>
+        <v>128998433</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489275</v>
+        <v>489243</v>
       </c>
       <c r="R16" t="n">
-        <v>6834885</v>
+        <v>6834808</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2118,26 +2118,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998305</v>
+        <v>128998457</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489249</v>
+        <v>489265</v>
       </c>
       <c r="R17" t="n">
-        <v>6834885</v>
+        <v>6834875</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2215,44 +2215,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128995421</v>
+        <v>128998567</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489351</v>
+        <v>489221</v>
       </c>
       <c r="R18" t="n">
-        <v>6834863</v>
+        <v>6834826</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 42180-2025 artfynd.xlsx
+++ b/artfynd/A 42180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995366</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995367</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995378</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995384</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995395</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995419</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995421</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998360</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998383</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998433</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998457</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,8 +2406,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>